--- a/transform/samples/files/lazada_orders.xlsx
+++ b/transform/samples/files/lazada_orders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L555"/>
+  <dimension ref="A1:N555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,16 @@
           <t>Shipping Address</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Refund Amount</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Refund Date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -533,6 +543,9 @@
           <t>195 Đường số 15, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -589,6 +602,9 @@
           <t>195 Đường số 15, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -645,6 +661,9 @@
           <t>107 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -701,6 +720,9 @@
           <t>8 Đường số 12, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -757,6 +779,9 @@
           <t>300 Đường số 29, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -813,6 +838,9 @@
           <t>193 Đường số 24, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -869,6 +897,9 @@
           <t>193 Đường số 24, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -925,6 +956,9 @@
           <t>8 Đường số 12, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -981,6 +1015,9 @@
           <t>8 Đường số 12, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1037,6 +1074,9 @@
           <t>8 Đường số 12, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1093,6 +1133,9 @@
           <t>207 Đường số 19, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1149,6 +1192,9 @@
           <t>244 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1205,6 +1251,9 @@
           <t>32 Đường số 14, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1261,6 +1310,9 @@
           <t>41 Đường số 5, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1317,6 +1369,9 @@
           <t>101 Đường số 4, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1373,6 +1428,9 @@
           <t>247 Đường số 16, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1429,6 +1487,9 @@
           <t>247 Đường số 16, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1485,6 +1546,9 @@
           <t>289 Đường số 8, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1541,6 +1605,9 @@
           <t>115 Đường số 18, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1597,6 +1664,9 @@
           <t>115 Đường số 18, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1653,6 +1723,9 @@
           <t>89 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1709,6 +1782,9 @@
           <t>100 Đường số 22, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1765,6 +1841,9 @@
           <t>100 Đường số 22, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1821,6 +1900,9 @@
           <t>100 Đường số 22, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1877,6 +1959,9 @@
           <t>300 Đường số 29, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1933,6 +2018,9 @@
           <t>196 Đường số 3, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1989,6 +2077,9 @@
           <t>196 Đường số 3, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2045,6 +2136,9 @@
           <t>196 Đường số 3, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2101,6 +2195,9 @@
           <t>121 Đường số 17, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2157,6 +2254,9 @@
           <t>121 Đường số 17, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2213,6 +2313,9 @@
           <t>93 Đường số 1, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2269,6 +2372,9 @@
           <t>93 Đường số 1, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2325,6 +2431,9 @@
           <t>235 Đường số 29, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2381,6 +2490,9 @@
           <t>235 Đường số 29, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2437,6 +2549,9 @@
           <t>235 Đường số 29, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2493,6 +2608,9 @@
           <t>116 Đường số 16, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2549,6 +2667,9 @@
           <t>116 Đường số 16, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2605,6 +2726,9 @@
           <t>200 Đường số 8, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2661,6 +2785,9 @@
           <t>200 Đường số 8, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2717,6 +2844,9 @@
           <t>72 Đường số 28, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2773,6 +2903,9 @@
           <t>72 Đường số 28, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2829,6 +2962,9 @@
           <t>197 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2885,6 +3021,9 @@
           <t>266 Đường số 17, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2941,6 +3080,9 @@
           <t>266 Đường số 17, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2997,6 +3139,9 @@
           <t>89 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3053,6 +3198,9 @@
           <t>33 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3109,6 +3257,9 @@
           <t>72 Đường số 28, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3165,6 +3316,9 @@
           <t>72 Đường số 28, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3221,6 +3375,9 @@
           <t>9 Đường số 11, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3277,6 +3434,9 @@
           <t>9 Đường số 11, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3333,6 +3493,9 @@
           <t>9 Đường số 11, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3389,6 +3552,9 @@
           <t>139 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3445,6 +3611,9 @@
           <t>289 Đường số 8, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3501,6 +3670,9 @@
           <t>83 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3557,6 +3729,9 @@
           <t>83 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3613,6 +3788,9 @@
           <t>83 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3669,6 +3847,9 @@
           <t>52 Đường số 5, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3725,6 +3906,9 @@
           <t>225 Đường số 2, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3781,6 +3965,9 @@
           <t>106 Đường số 7, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3837,6 +4024,9 @@
           <t>228 Đường số 10, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3893,6 +4083,9 @@
           <t>120 Đường số 28, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3949,6 +4142,9 @@
           <t>120 Đường số 28, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4005,6 +4201,9 @@
           <t>193 Đường số 24, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4061,6 +4260,9 @@
           <t>49 Đường số 30, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4117,6 +4319,9 @@
           <t>49 Đường số 30, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4173,6 +4378,9 @@
           <t>49 Đường số 30, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4229,6 +4437,9 @@
           <t>49 Đường số 30, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4285,6 +4496,9 @@
           <t>218 Đường số 4, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4341,6 +4555,9 @@
           <t>218 Đường số 4, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4397,6 +4614,9 @@
           <t>218 Đường số 4, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4453,6 +4673,9 @@
           <t>61 Đường số 17, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4509,6 +4732,9 @@
           <t>26 Đường số 29, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4565,6 +4791,9 @@
           <t>26 Đường số 29, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4621,6 +4850,9 @@
           <t>26 Đường số 29, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4677,6 +4909,9 @@
           <t>33 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4733,6 +4968,9 @@
           <t>266 Đường số 14, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4789,6 +5027,9 @@
           <t>218 Đường số 4, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4845,6 +5086,9 @@
           <t>200 Đường số 8, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4901,6 +5145,9 @@
           <t>76 Đường số 1, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4957,6 +5204,9 @@
           <t>288 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5013,6 +5263,9 @@
           <t>31 Đường số 14, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5069,6 +5322,9 @@
           <t>190 Đường số 9, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5125,6 +5381,9 @@
           <t>218 Đường số 4, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5181,6 +5440,9 @@
           <t>218 Đường số 4, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5237,6 +5499,9 @@
           <t>218 Đường số 4, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5293,6 +5558,9 @@
           <t>27 Đường số 25, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5349,6 +5617,9 @@
           <t>116 Đường số 14, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5405,6 +5676,9 @@
           <t>116 Đường số 14, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5461,6 +5735,9 @@
           <t>121 Đường số 17, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5517,6 +5794,9 @@
           <t>160 Đường số 24, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5573,6 +5853,9 @@
           <t>111 Đường số 20, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5629,6 +5912,9 @@
           <t>233 Đường số 10, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5685,6 +5971,9 @@
           <t>116 Đường số 14, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5741,6 +6030,9 @@
           <t>138 Đường số 18, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5797,6 +6089,9 @@
           <t>138 Đường số 18, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5853,6 +6148,9 @@
           <t>138 Đường số 18, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5909,6 +6207,9 @@
           <t>189 Đường số 2, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5965,6 +6266,9 @@
           <t>189 Đường số 2, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6021,6 +6325,9 @@
           <t>218 Đường số 4, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6077,6 +6384,9 @@
           <t>26 Đường số 29, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6133,6 +6443,9 @@
           <t>248 Đường số 29, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6189,6 +6502,9 @@
           <t>248 Đường số 29, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6245,6 +6561,9 @@
           <t>83 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6301,6 +6620,14 @@
           <t>125 Đường số 19, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M105" t="n">
+        <v>94000</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>2026-08-11 18:28</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6357,6 +6684,9 @@
           <t>125 Đường số 19, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6413,6 +6743,9 @@
           <t>106 Đường số 7, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6469,6 +6802,9 @@
           <t>103 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6525,6 +6861,9 @@
           <t>103 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6581,6 +6920,9 @@
           <t>20 Đường số 27, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6637,6 +6979,9 @@
           <t>100 Đường số 22, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6693,6 +7038,9 @@
           <t>100 Đường số 22, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6749,6 +7097,9 @@
           <t>190 Đường số 9, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6805,6 +7156,9 @@
           <t>83 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6861,6 +7215,9 @@
           <t>182 Đường số 8, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6917,6 +7274,9 @@
           <t>200 Đường số 15, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6973,6 +7333,9 @@
           <t>286 Đường số 10, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7029,6 +7392,9 @@
           <t>111 Đường số 20, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7085,6 +7451,9 @@
           <t>287 Đường số 23, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7141,6 +7510,9 @@
           <t>287 Đường số 23, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7197,6 +7569,9 @@
           <t>83 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7253,6 +7628,9 @@
           <t>160 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7309,6 +7687,9 @@
           <t>160 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7365,6 +7746,9 @@
           <t>250 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7421,6 +7805,9 @@
           <t>289 Đường số 8, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7477,6 +7864,9 @@
           <t>8 Đường số 30, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7533,6 +7923,9 @@
           <t>8 Đường số 30, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7589,6 +7982,9 @@
           <t>183 Đường số 28, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7645,6 +8041,9 @@
           <t>200 Đường số 8, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7701,6 +8100,9 @@
           <t>200 Đường số 8, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7757,6 +8159,9 @@
           <t>266 Đường số 14, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7813,6 +8218,9 @@
           <t>266 Đường số 14, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7869,6 +8277,9 @@
           <t>244 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7925,6 +8336,9 @@
           <t>244 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7981,6 +8395,9 @@
           <t>244 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8037,6 +8454,9 @@
           <t>115 Đường số 18, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8093,6 +8513,9 @@
           <t>115 Đường số 18, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8149,6 +8572,9 @@
           <t>8 Đường số 12, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8205,6 +8631,9 @@
           <t>101 Đường số 4, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8261,6 +8690,9 @@
           <t>101 Đường số 4, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8317,6 +8749,9 @@
           <t>101 Đường số 4, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8373,6 +8808,9 @@
           <t>244 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8429,6 +8867,9 @@
           <t>266 Đường số 17, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8485,6 +8926,9 @@
           <t>292 Đường số 5, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8541,6 +8985,9 @@
           <t>233 Đường số 10, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8597,6 +9044,9 @@
           <t>190 Đường số 9, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8653,6 +9103,9 @@
           <t>190 Đường số 9, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8709,6 +9162,9 @@
           <t>100 Đường số 14, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8765,6 +9221,9 @@
           <t>100 Đường số 14, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8821,6 +9280,9 @@
           <t>100 Đường số 14, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8877,6 +9339,14 @@
           <t>235 Đường số 9, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M151" t="n">
+        <v>208000</v>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:25</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8933,6 +9403,9 @@
           <t>248 Đường số 29, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8989,6 +9462,9 @@
           <t>45 Đường số 6, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9045,6 +9521,9 @@
           <t>45 Đường số 6, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9101,6 +9580,9 @@
           <t>45 Đường số 6, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9157,6 +9639,9 @@
           <t>287 Đường số 23, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9213,6 +9698,9 @@
           <t>287 Đường số 23, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9269,6 +9757,9 @@
           <t>287 Đường số 23, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9325,6 +9816,9 @@
           <t>182 Đường số 8, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9381,6 +9875,9 @@
           <t>182 Đường số 8, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9437,6 +9934,9 @@
           <t>182 Đường số 8, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9493,6 +9993,9 @@
           <t>15 Đường số 2, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9549,6 +10052,9 @@
           <t>15 Đường số 2, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9605,6 +10111,9 @@
           <t>116 Đường số 16, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9661,6 +10170,9 @@
           <t>52 Đường số 5, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9717,6 +10229,9 @@
           <t>52 Đường số 5, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9773,6 +10288,9 @@
           <t>52 Đường số 5, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9829,6 +10347,9 @@
           <t>300 Đường số 29, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9885,6 +10406,9 @@
           <t>300 Đường số 29, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9941,6 +10465,9 @@
           <t>300 Đường số 29, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9997,6 +10524,9 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10053,6 +10583,9 @@
           <t>280 Đường số 21, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10109,6 +10642,9 @@
           <t>50 Đường số 24, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10165,6 +10701,9 @@
           <t>139 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10221,6 +10760,9 @@
           <t>139 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10277,6 +10819,9 @@
           <t>139 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10333,6 +10878,9 @@
           <t>33 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10389,6 +10937,9 @@
           <t>33 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10445,6 +10996,14 @@
           <t>276 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M179" t="n">
+        <v>189000</v>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:04</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10501,6 +11060,9 @@
           <t>276 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10557,6 +11119,9 @@
           <t>276 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10613,6 +11178,9 @@
           <t>52 Đường số 5, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10669,6 +11237,9 @@
           <t>89 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10725,6 +11296,9 @@
           <t>165 Đường số 26, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10781,6 +11355,9 @@
           <t>45 Đường số 6, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10837,6 +11414,9 @@
           <t>45 Đường số 6, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10893,6 +11473,9 @@
           <t>45 Đường số 6, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10949,6 +11532,9 @@
           <t>45 Đường số 6, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11005,6 +11591,9 @@
           <t>175 Đường số 18, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11061,6 +11650,9 @@
           <t>175 Đường số 18, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11117,6 +11709,9 @@
           <t>280 Đường số 21, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11173,6 +11768,9 @@
           <t>280 Đường số 21, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11229,6 +11827,9 @@
           <t>280 Đường số 21, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11285,6 +11886,9 @@
           <t>298 Đường số 17, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11341,6 +11945,9 @@
           <t>298 Đường số 17, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11397,6 +12004,9 @@
           <t>189 Đường số 2, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11453,6 +12063,9 @@
           <t>189 Đường số 2, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11509,6 +12122,9 @@
           <t>220 Đường số 1, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -11565,6 +12181,9 @@
           <t>220 Đường số 1, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -11621,6 +12240,9 @@
           <t>282 Đường số 8, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -11677,6 +12299,9 @@
           <t>282 Đường số 8, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -11733,6 +12358,9 @@
           <t>282 Đường số 8, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11789,6 +12417,9 @@
           <t>139 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11845,6 +12476,9 @@
           <t>139 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11901,6 +12535,9 @@
           <t>139 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11957,6 +12594,9 @@
           <t>160 Đường số 24, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12013,6 +12653,9 @@
           <t>160 Đường số 24, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12069,6 +12712,9 @@
           <t>160 Đường số 24, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12125,6 +12771,9 @@
           <t>237 Đường số 27, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12181,6 +12830,9 @@
           <t>100 Đường số 14, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12237,6 +12889,9 @@
           <t>31 Đường số 18, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12293,6 +12948,9 @@
           <t>154 Đường số 19, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12349,6 +13007,9 @@
           <t>154 Đường số 19, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12405,6 +13066,9 @@
           <t>233 Đường số 10, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12461,6 +13125,14 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M215" t="n">
+        <v>66000</v>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>2026-08-30 01:27</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12517,6 +13189,9 @@
           <t>234 Đường số 29, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12573,6 +13248,9 @@
           <t>191 Đường số 1, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12629,6 +13307,9 @@
           <t>191 Đường số 1, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12685,6 +13366,9 @@
           <t>191 Đường số 1, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -12741,6 +13425,9 @@
           <t>231 Đường số 2, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -12797,6 +13484,9 @@
           <t>175 Đường số 18, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -12853,6 +13543,9 @@
           <t>33 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12909,6 +13602,9 @@
           <t>33 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M223" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12965,6 +13661,9 @@
           <t>125 Đường số 19, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13021,6 +13720,9 @@
           <t>288 Đường số 5, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13077,6 +13779,9 @@
           <t>248 Đường số 29, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M226" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13133,6 +13838,9 @@
           <t>27 Đường số 25, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13189,6 +13897,9 @@
           <t>27 Đường số 25, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13245,6 +13956,9 @@
           <t>88 Đường số 30, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M229" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13301,6 +14015,9 @@
           <t>88 Đường số 30, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M230" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13357,6 +14074,9 @@
           <t>213 Đường số 28, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M231" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13413,6 +14133,9 @@
           <t>26 Đường số 29, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M232" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13469,6 +14192,9 @@
           <t>26 Đường số 29, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M233" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13525,6 +14251,9 @@
           <t>139 Đường số 10, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M234" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13581,6 +14310,9 @@
           <t>294 Đường số 8, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M235" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -13637,6 +14369,9 @@
           <t>280 Đường số 21, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M236" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13693,6 +14428,9 @@
           <t>200 Đường số 22, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -13749,6 +14487,9 @@
           <t>200 Đường số 22, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M238" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -13805,6 +14546,9 @@
           <t>157 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M239" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -13861,6 +14605,9 @@
           <t>157 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13917,6 +14664,9 @@
           <t>9 Đường số 11, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M241" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -13973,6 +14723,9 @@
           <t>9 Đường số 11, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M242" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14029,6 +14782,9 @@
           <t>9 Đường số 11, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M243" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14085,6 +14841,9 @@
           <t>9 Đường số 11, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M244" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14141,6 +14900,9 @@
           <t>93 Đường số 1, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M245" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14197,6 +14959,9 @@
           <t>93 Đường số 1, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M246" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14253,6 +15018,9 @@
           <t>93 Đường số 1, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M247" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14309,6 +15077,9 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M248" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14365,6 +15136,9 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M249" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -14421,6 +15195,9 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M250" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14477,6 +15254,9 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M251" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -14533,6 +15313,9 @@
           <t>190 Đường số 9, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M252" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -14589,6 +15372,9 @@
           <t>244 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M253" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -14645,6 +15431,9 @@
           <t>49 Đường số 30, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M254" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -14701,6 +15490,9 @@
           <t>49 Đường số 30, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -14757,6 +15549,9 @@
           <t>101 Đường số 4, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M256" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14813,6 +15608,9 @@
           <t>52 Đường số 3, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M257" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -14869,6 +15667,9 @@
           <t>52 Đường số 3, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M258" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -14925,6 +15726,9 @@
           <t>72 Đường số 28, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M259" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -14981,6 +15785,9 @@
           <t>213 Đường số 28, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M260" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15037,6 +15844,9 @@
           <t>3 Đường số 10, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M261" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -15093,6 +15903,9 @@
           <t>31 Đường số 18, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M262" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15149,6 +15962,9 @@
           <t>15 Đường số 2, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M263" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -15205,6 +16021,9 @@
           <t>234 Đường số 29, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M264" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -15261,6 +16080,9 @@
           <t>234 Đường số 29, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M265" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15317,6 +16139,9 @@
           <t>234 Đường số 29, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M266" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -15373,6 +16198,9 @@
           <t>103 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M267" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -15429,6 +16257,9 @@
           <t>196 Đường số 3, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M268" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -15485,6 +16316,9 @@
           <t>196 Đường số 3, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M269" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -15541,6 +16375,9 @@
           <t>43 Đường số 8, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M270" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -15597,6 +16434,9 @@
           <t>76 Đường số 1, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M271" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -15653,6 +16493,9 @@
           <t>110 Đường số 1, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -15709,6 +16552,9 @@
           <t>276 Đường số 5, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -15765,6 +16611,9 @@
           <t>189 Đường số 2, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -15821,6 +16670,9 @@
           <t>189 Đường số 2, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -15877,6 +16729,9 @@
           <t>207 Đường số 19, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -15933,6 +16788,9 @@
           <t>250 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -15989,6 +16847,9 @@
           <t>191 Đường số 1, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -16045,6 +16906,9 @@
           <t>24 Đường số 10, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -16101,6 +16965,9 @@
           <t>24 Đường số 10, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -16157,6 +17024,9 @@
           <t>287 Đường số 23, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -16213,6 +17083,9 @@
           <t>287 Đường số 23, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M282" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -16269,6 +17142,9 @@
           <t>218 Đường số 4, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M283" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -16325,6 +17201,9 @@
           <t>83 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M284" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -16381,6 +17260,9 @@
           <t>5 Đường số 12, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M285" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -16437,6 +17319,9 @@
           <t>5 Đường số 12, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M286" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -16493,6 +17378,9 @@
           <t>139 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M287" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -16549,6 +17437,9 @@
           <t>200 Đường số 22, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M288" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -16605,6 +17496,14 @@
           <t>100 Đường số 22, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M289" t="n">
+        <v>94000</v>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>2026-09-11 17:10</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -16661,6 +17560,9 @@
           <t>107 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M290" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -16717,6 +17619,9 @@
           <t>107 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M291" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -16773,6 +17678,9 @@
           <t>107 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M292" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -16829,6 +17737,9 @@
           <t>189 Đường số 2, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M293" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -16885,6 +17796,9 @@
           <t>127 Đường số 27, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M294" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -16941,6 +17855,9 @@
           <t>127 Đường số 27, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M295" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -16997,6 +17914,9 @@
           <t>127 Đường số 27, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M296" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -17053,6 +17973,9 @@
           <t>258 Đường số 16, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M297" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -17109,6 +18032,9 @@
           <t>177 Đường số 14, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M298" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -17165,6 +18091,9 @@
           <t>177 Đường số 14, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -17221,6 +18150,9 @@
           <t>177 Đường số 14, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M300" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -17277,6 +18209,9 @@
           <t>3 Đường số 10, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M301" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -17333,6 +18268,9 @@
           <t>191 Đường số 1, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M302" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -17389,6 +18327,9 @@
           <t>127 Đường số 27, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M303" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -17445,6 +18386,9 @@
           <t>127 Đường số 27, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M304" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -17501,6 +18445,9 @@
           <t>127 Đường số 27, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M305" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -17557,6 +18504,9 @@
           <t>100 Đường số 14, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M306" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -17613,6 +18563,9 @@
           <t>100 Đường số 14, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M307" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -17669,6 +18622,9 @@
           <t>100 Đường số 14, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M308" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -17725,6 +18681,9 @@
           <t>200 Đường số 15, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M309" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -17781,6 +18740,9 @@
           <t>107 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M310" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -17837,6 +18799,9 @@
           <t>107 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M311" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -17893,6 +18858,9 @@
           <t>287 Đường số 23, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M312" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -17949,6 +18917,9 @@
           <t>234 Đường số 29, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M313" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -18005,6 +18976,9 @@
           <t>139 Đường số 10, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M314" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -18061,6 +19035,9 @@
           <t>139 Đường số 10, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M315" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -18117,6 +19094,9 @@
           <t>101 Đường số 4, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M316" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -18173,6 +19153,9 @@
           <t>101 Đường số 4, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M317" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -18229,6 +19212,9 @@
           <t>182 Đường số 8, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M318" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -18285,6 +19271,9 @@
           <t>171 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M319" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -18341,6 +19330,9 @@
           <t>225 Đường số 2, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M320" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -18397,6 +19389,9 @@
           <t>107 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M321" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -18453,6 +19448,9 @@
           <t>107 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M322" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -18509,6 +19507,9 @@
           <t>276 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M323" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -18565,6 +19566,9 @@
           <t>110 Đường số 1, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M324" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -18621,6 +19625,9 @@
           <t>87 Đường số 9, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M325" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -18677,6 +19684,9 @@
           <t>250 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M326" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -18733,6 +19743,9 @@
           <t>165 Đường số 26, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M327" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -18789,6 +19802,9 @@
           <t>175 Đường số 18, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M328" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -18845,6 +19861,9 @@
           <t>175 Đường số 18, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M329" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -18901,6 +19920,9 @@
           <t>152 Đường số 12, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M330" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -18957,6 +19979,9 @@
           <t>43 Đường số 8, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M331" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -19013,6 +20038,9 @@
           <t>225 Đường số 2, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M332" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -19069,6 +20097,9 @@
           <t>225 Đường số 2, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M333" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -19125,6 +20156,9 @@
           <t>16 Đường số 15, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M334" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -19181,6 +20215,9 @@
           <t>139 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M335" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -19237,6 +20274,9 @@
           <t>197 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M336" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -19293,6 +20333,9 @@
           <t>197 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M337" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -19349,6 +20392,9 @@
           <t>197 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M338" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -19405,6 +20451,9 @@
           <t>197 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M339" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -19461,6 +20510,9 @@
           <t>33 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M340" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -19517,6 +20569,9 @@
           <t>33 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M341" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -19573,6 +20628,9 @@
           <t>33 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M342" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -19629,6 +20687,9 @@
           <t>33 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M343" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -19685,6 +20746,9 @@
           <t>31 Đường số 18, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M344" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -19741,6 +20805,9 @@
           <t>72 Đường số 28, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M345" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -19797,6 +20864,9 @@
           <t>72 Đường số 28, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M346" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -19853,6 +20923,9 @@
           <t>93 Đường số 1, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M347" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -19909,6 +20982,9 @@
           <t>93 Đường số 1, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M348" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -19965,6 +21041,9 @@
           <t>157 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M349" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -20021,6 +21100,9 @@
           <t>157 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M350" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -20077,6 +21159,9 @@
           <t>100 Đường số 14, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M351" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -20133,6 +21218,9 @@
           <t>248 Đường số 29, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M352" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -20189,6 +21277,9 @@
           <t>116 Đường số 14, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M353" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -20245,6 +21336,9 @@
           <t>125 Đường số 19, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M354" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -20301,6 +21395,9 @@
           <t>125 Đường số 19, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M355" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -20357,6 +21454,9 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M356" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -20413,6 +21513,9 @@
           <t>127 Đường số 27, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M357" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -20469,6 +21572,9 @@
           <t>142 Đường số 14, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M358" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -20525,6 +21631,9 @@
           <t>142 Đường số 14, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M359" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -20581,6 +21690,9 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M360" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -20637,6 +21749,9 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M361" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -20693,6 +21808,9 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M362" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -20749,6 +21867,14 @@
           <t>228 Đường số 10, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M363" t="n">
+        <v>275000</v>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:20</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -20805,6 +21931,9 @@
           <t>228 Đường số 10, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M364" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -20861,6 +21990,9 @@
           <t>289 Đường số 8, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M365" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -20917,6 +22049,9 @@
           <t>213 Đường số 28, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M366" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -20973,6 +22108,9 @@
           <t>213 Đường số 28, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M367" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -21029,6 +22167,9 @@
           <t>213 Đường số 28, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M368" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -21085,6 +22226,9 @@
           <t>288 Đường số 5, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M369" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -21141,6 +22285,9 @@
           <t>298 Đường số 17, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M370" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -21197,6 +22344,9 @@
           <t>152 Đường số 12, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M371" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -21253,6 +22403,9 @@
           <t>152 Đường số 12, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M372" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -21309,6 +22462,9 @@
           <t>152 Đường số 12, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M373" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -21365,6 +22521,9 @@
           <t>43 Đường số 8, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M374" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -21421,6 +22580,9 @@
           <t>50 Đường số 24, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M375" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -21477,6 +22639,9 @@
           <t>247 Đường số 16, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M376" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -21533,6 +22698,9 @@
           <t>247 Đường số 16, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M377" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -21589,6 +22757,9 @@
           <t>247 Đường số 16, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M378" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -21645,6 +22816,9 @@
           <t>175 Đường số 18, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M379" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -21701,6 +22875,9 @@
           <t>175 Đường số 18, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M380" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -21757,6 +22934,9 @@
           <t>226 Đường số 29, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M381" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -21813,6 +22993,9 @@
           <t>152 Đường số 12, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M382" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -21869,6 +23052,9 @@
           <t>32 Đường số 14, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M383" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -21925,6 +23111,9 @@
           <t>32 Đường số 14, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M384" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -21981,6 +23170,9 @@
           <t>41 Đường số 5, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M385" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -22037,6 +23229,9 @@
           <t>41 Đường số 5, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M386" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -22093,6 +23288,9 @@
           <t>116 Đường số 16, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M387" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -22149,6 +23347,9 @@
           <t>250 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M388" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -22205,6 +23406,9 @@
           <t>250 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M389" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -22261,6 +23465,9 @@
           <t>250 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M390" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -22317,6 +23524,9 @@
           <t>190 Đường số 1, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M391" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -22373,6 +23583,9 @@
           <t>190 Đường số 1, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M392" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -22429,6 +23642,9 @@
           <t>190 Đường số 1, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M393" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -22485,6 +23701,14 @@
           <t>93 Đường số 1, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M394" t="n">
+        <v>151000</v>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>2026-09-26 14:24</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -22541,6 +23765,9 @@
           <t>110 Đường số 26, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M395" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -22597,6 +23824,9 @@
           <t>110 Đường số 26, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M396" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -22653,6 +23883,9 @@
           <t>200 Đường số 22, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M397" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -22709,6 +23942,9 @@
           <t>15 Đường số 2, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M398" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -22765,6 +24001,9 @@
           <t>196 Đường số 3, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M399" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -22821,6 +24060,9 @@
           <t>235 Đường số 9, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M400" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -22877,6 +24119,9 @@
           <t>93 Đường số 1, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M401" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -22933,6 +24178,9 @@
           <t>282 Đường số 8, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M402" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -22989,6 +24237,9 @@
           <t>282 Đường số 8, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M403" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -23045,6 +24296,9 @@
           <t>282 Đường số 8, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M404" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -23101,6 +24355,9 @@
           <t>282 Đường số 8, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M405" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -23157,6 +24414,9 @@
           <t>282 Đường số 8, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M406" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -23213,6 +24473,9 @@
           <t>235 Đường số 29, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M407" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -23269,6 +24532,9 @@
           <t>107 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M408" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -23325,6 +24591,9 @@
           <t>88 Đường số 30, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M409" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -23381,6 +24650,9 @@
           <t>76 Đường số 8, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M410" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -23437,6 +24709,9 @@
           <t>76 Đường số 8, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M411" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -23493,6 +24768,9 @@
           <t>165 Đường số 26, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M412" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -23549,6 +24827,9 @@
           <t>200 Đường số 15, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M413" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -23605,6 +24886,9 @@
           <t>200 Đường số 15, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M414" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -23661,6 +24945,9 @@
           <t>200 Đường số 15, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M415" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -23717,6 +25004,9 @@
           <t>200 Đường số 8, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M416" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -23773,6 +25063,9 @@
           <t>200 Đường số 8, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M417" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -23829,6 +25122,9 @@
           <t>288 Đường số 5, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M418" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -23885,6 +25181,9 @@
           <t>160 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M419" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -23941,6 +25240,9 @@
           <t>226 Đường số 29, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M420" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -23997,6 +25299,9 @@
           <t>226 Đường số 29, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M421" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -24053,6 +25358,9 @@
           <t>249 Đường số 10, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M422" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -24109,6 +25417,9 @@
           <t>249 Đường số 10, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M423" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -24165,6 +25476,9 @@
           <t>31 Đường số 18, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M424" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -24221,6 +25535,9 @@
           <t>200 Đường số 22, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M425" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -24277,6 +25594,9 @@
           <t>200 Đường số 22, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M426" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -24333,6 +25653,9 @@
           <t>200 Đường số 22, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M427" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -24389,6 +25712,14 @@
           <t>265 Đường số 27, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M428" t="n">
+        <v>66000</v>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>2026-10-03 19:25</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -24445,6 +25776,9 @@
           <t>265 Đường số 27, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M429" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -24501,6 +25835,9 @@
           <t>265 Đường số 27, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M430" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -24557,6 +25894,9 @@
           <t>265 Đường số 27, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M431" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -24613,6 +25953,9 @@
           <t>127 Đường số 27, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M432" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -24669,6 +26012,9 @@
           <t>200 Đường số 8, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M433" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -24725,6 +26071,9 @@
           <t>200 Đường số 8, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M434" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -24781,6 +26130,9 @@
           <t>182 Đường số 8, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M435" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -24837,6 +26189,9 @@
           <t>271 Đường số 28, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M436" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -24893,6 +26248,9 @@
           <t>157 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M437" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -24949,6 +26307,9 @@
           <t>139 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M438" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -25005,6 +26366,9 @@
           <t>116 Đường số 14, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M439" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -25061,6 +26425,9 @@
           <t>116 Đường số 14, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M440" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -25117,6 +26484,9 @@
           <t>116 Đường số 14, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M441" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -25173,6 +26543,9 @@
           <t>116 Đường số 14, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M442" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -25229,6 +26602,9 @@
           <t>116 Đường số 14, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M443" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -25285,6 +26661,9 @@
           <t>116 Đường số 14, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M444" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -25341,6 +26720,9 @@
           <t>89 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M445" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -25397,6 +26779,9 @@
           <t>89 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M446" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -25453,6 +26838,9 @@
           <t>89 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M447" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -25509,6 +26897,9 @@
           <t>100 Đường số 22, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M448" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -25565,6 +26956,9 @@
           <t>43 Đường số 8, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M449" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -25621,6 +27015,9 @@
           <t>8 Đường số 12, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M450" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -25677,6 +27074,9 @@
           <t>8 Đường số 12, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M451" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -25733,6 +27133,9 @@
           <t>8 Đường số 12, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M452" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -25789,6 +27192,9 @@
           <t>200 Đường số 22, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M453" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -25845,6 +27251,9 @@
           <t>189 Đường số 2, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M454" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -25901,6 +27310,9 @@
           <t>189 Đường số 2, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M455" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -25957,6 +27369,9 @@
           <t>238 Đường số 18, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M456" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -26013,6 +27428,9 @@
           <t>83 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M457" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -26069,6 +27487,9 @@
           <t>83 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M458" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -26125,6 +27546,9 @@
           <t>139 Đường số 10, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M459" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -26181,6 +27605,9 @@
           <t>111 Đường số 20, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M460" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -26237,6 +27664,9 @@
           <t>111 Đường số 20, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M461" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -26293,6 +27723,9 @@
           <t>106 Đường số 7, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M462" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -26349,6 +27782,9 @@
           <t>106 Đường số 7, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M463" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -26405,6 +27841,9 @@
           <t>160 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M464" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -26461,6 +27900,9 @@
           <t>189 Đường số 2, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M465" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -26517,6 +27959,9 @@
           <t>121 Đường số 17, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M466" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -26573,6 +28018,9 @@
           <t>157 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M467" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -26629,6 +28077,9 @@
           <t>157 Đường số 7, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M468" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -26685,6 +28136,9 @@
           <t>15 Đường số 2, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M469" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -26741,6 +28195,9 @@
           <t>288 Đường số 11, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M470" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -26797,6 +28254,9 @@
           <t>27 Đường số 25, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M471" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -26853,6 +28313,9 @@
           <t>138 Đường số 20, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M472" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -26909,6 +28372,9 @@
           <t>116 Đường số 16, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M473" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -26965,6 +28431,9 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M474" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -27021,6 +28490,9 @@
           <t>190 Đường số 1, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M475" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -27077,6 +28549,9 @@
           <t>196 Đường số 3, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M476" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -27133,6 +28608,9 @@
           <t>115 Đường số 18, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M477" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -27189,6 +28667,9 @@
           <t>106 Đường số 7, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M478" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -27245,6 +28726,9 @@
           <t>106 Đường số 7, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M479" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -27301,6 +28785,9 @@
           <t>250 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M480" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -27357,6 +28844,9 @@
           <t>250 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M481" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -27413,6 +28903,9 @@
           <t>250 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M482" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -27469,6 +28962,9 @@
           <t>250 Đường số 29, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M483" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -27525,6 +29021,9 @@
           <t>200 Đường số 8, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M484" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -27581,6 +29080,9 @@
           <t>93 Đường số 1, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M485" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -27637,6 +29139,9 @@
           <t>93 Đường số 1, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M486" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -27693,6 +29198,9 @@
           <t>93 Đường số 1, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M487" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -27749,6 +29257,9 @@
           <t>106 Đường số 7, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M488" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -27805,6 +29316,9 @@
           <t>107 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M489" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -27861,6 +29375,9 @@
           <t>142 Đường số 14, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M490" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -27917,6 +29434,9 @@
           <t>142 Đường số 14, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M491" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -27973,6 +29493,9 @@
           <t>160 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M492" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -28029,6 +29552,9 @@
           <t>160 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M493" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -28085,6 +29611,9 @@
           <t>160 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M494" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -28141,6 +29670,9 @@
           <t>15 Đường số 2, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M495" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -28197,6 +29729,9 @@
           <t>282 Đường số 8, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M496" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -28253,6 +29788,9 @@
           <t>197 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M497" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -28309,6 +29847,9 @@
           <t>197 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M498" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -28365,6 +29906,9 @@
           <t>106 Đường số 7, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M499" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -28421,6 +29965,9 @@
           <t>33 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M500" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -28477,6 +30024,9 @@
           <t>33 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M501" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -28533,6 +30083,9 @@
           <t>33 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M502" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -28589,6 +30142,9 @@
           <t>209 Đường số 30, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M503" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -28645,6 +30201,9 @@
           <t>209 Đường số 30, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M504" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -28701,6 +30260,9 @@
           <t>139 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M505" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -28757,6 +30319,9 @@
           <t>139 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M506" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -28813,6 +30378,9 @@
           <t>139 Đường số 17, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M507" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -28869,6 +30437,9 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M508" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -28925,6 +30496,9 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M509" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -28981,6 +30555,9 @@
           <t>178 Đường số 3, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M510" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -29037,6 +30614,9 @@
           <t>31 Đường số 14, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M511" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -29093,6 +30673,9 @@
           <t>276 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M512" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -29149,6 +30732,9 @@
           <t>200 Đường số 22, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M513" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -29205,6 +30791,9 @@
           <t>247 Đường số 16, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M514" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -29261,6 +30850,9 @@
           <t>116 Đường số 14, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M515" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -29317,6 +30909,9 @@
           <t>116 Đường số 14, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M516" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -29373,6 +30968,9 @@
           <t>218 Đường số 4, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M517" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -29429,6 +31027,9 @@
           <t>235 Đường số 29, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M518" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -29485,6 +31086,9 @@
           <t>235 Đường số 29, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M519" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -29541,6 +31145,9 @@
           <t>288 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M520" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -29597,6 +31204,9 @@
           <t>288 Đường số 16, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M521" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -29653,6 +31263,9 @@
           <t>107 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M522" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -29709,6 +31322,9 @@
           <t>107 Đường số 18, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M523" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -29765,6 +31381,9 @@
           <t>110 Đường số 26, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M524" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -29821,6 +31440,9 @@
           <t>138 Đường số 18, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M525" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -29877,6 +31499,9 @@
           <t>138 Đường số 18, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M526" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -29933,6 +31558,9 @@
           <t>138 Đường số 18, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M527" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -29989,6 +31617,9 @@
           <t>292 Đường số 5, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M528" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -30045,6 +31676,9 @@
           <t>292 Đường số 5, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M529" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -30101,6 +31735,9 @@
           <t>292 Đường số 5, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M530" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -30157,6 +31794,9 @@
           <t>209 Đường số 30, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M531" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -30213,6 +31853,9 @@
           <t>209 Đường số 30, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M532" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -30269,6 +31912,9 @@
           <t>209 Đường số 30, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M533" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -30325,6 +31971,9 @@
           <t>209 Đường số 30, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M534" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -30381,6 +32030,9 @@
           <t>199 Đường số 25, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M535" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -30437,6 +32089,9 @@
           <t>160 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M536" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -30493,6 +32148,9 @@
           <t>160 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M537" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -30549,6 +32207,9 @@
           <t>160 Đường số 4, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M538" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -30605,6 +32266,9 @@
           <t>15 Đường số 2, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M539" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -30661,6 +32325,9 @@
           <t>120 Đường số 28, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M540" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -30717,6 +32384,9 @@
           <t>120 Đường số 28, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M541" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -30773,6 +32443,9 @@
           <t>120 Đường số 28, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M542" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -30829,6 +32502,9 @@
           <t>116 Đường số 16, Quận 1, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M543" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -30885,6 +32561,9 @@
           <t>218 Đường số 4, Hải Châu, Đà Nẵng</t>
         </is>
       </c>
+      <c r="M544" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -30941,6 +32620,9 @@
           <t>110 Đường số 26, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M545" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -30997,6 +32679,9 @@
           <t>276 Đường số 5, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M546" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -31053,6 +32738,9 @@
           <t>276 Đường số 5, Thủ Đức, TP. Hồ Chí Minh</t>
         </is>
       </c>
+      <c r="M547" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -31109,6 +32797,9 @@
           <t>15 Đường số 2, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M548" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -31165,6 +32856,9 @@
           <t>287 Đường số 23, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M549" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -31221,6 +32915,9 @@
           <t>287 Đường số 23, Đống Đa, Hà Nội</t>
         </is>
       </c>
+      <c r="M550" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -31277,6 +32974,9 @@
           <t>249 Đường số 10, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M551" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -31333,6 +33033,9 @@
           <t>288 Đường số 30, Ninh Kiều, Cần Thơ</t>
         </is>
       </c>
+      <c r="M552" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -31389,6 +33092,9 @@
           <t>191 Đường số 1, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M553" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -31445,6 +33151,9 @@
           <t>191 Đường số 1, Cầu Giấy, Hà Nội</t>
         </is>
       </c>
+      <c r="M554" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -31500,6 +33209,9 @@
         <is>
           <t>191 Đường số 1, Cầu Giấy, Hà Nội</t>
         </is>
+      </c>
+      <c r="M555" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
